--- a/assets/files/templates/SafePlum_council_minutes.xlsx
+++ b/assets/files/templates/SafePlum_council_minutes.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="84">
   <si>
     <t xml:space="preserve">안전 및 보건에 관한 협의체 회의록 — 작성 안내</t>
   </si>
@@ -2678,9 +2678,6 @@
       </rPr>
       <t xml:space="preserve">개소 설치</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-10</t>
   </si>
   <si>
     <r>
@@ -4227,8 +4224,8 @@
       <c r="E36" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="23" t="s">
-        <v>71</v>
+      <c r="F36" s="23" t="n">
+        <v>46336</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>38</v>
@@ -4267,7 +4264,7 @@
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -4382,7 +4379,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4392,7 +4389,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4402,11 +4399,11 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="17"/>
@@ -4414,22 +4411,22 @@
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>81</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4590,7 +4587,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4601,7 +4598,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>

--- a/assets/files/templates/SafePlum_council_minutes.xlsx
+++ b/assets/files/templates/SafePlum_council_minutes.xlsx
@@ -3719,12 +3719,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -3737,12 +3737,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
